--- a/reports/一级子公司B_利润表_2025-02.xlsx
+++ b/reports/一级子公司B_利润表_2025-02.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>42324199</v>
+        <v>56330630</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>0</v>
+        <v>12455738</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>0</v>
+        <v>24899008</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>0</v>
+        <v>177053</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>0</v>
+        <v>353689</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>0</v>
+        <v>159295</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>0</v>
+        <v>318528</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>0</v>
+        <v>132570</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>0</v>
+        <v>265359</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>0</v>
+        <v>123475</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>0</v>
+        <v>247371</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>0</v>
+        <v>70382</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>0</v>
+        <v>141087</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>0</v>
+        <v>52658</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>0</v>
+        <v>105576</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>42324199</v>
+        <v>55615197</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0</v>
+        <v>11740305</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>0</v>
+        <v>6998308</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>0</v>
+        <v>14005610</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>0</v>
+        <v>1050714</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>0</v>
+        <v>2100596</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>0</v>
+        <v>526306</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>0</v>
+        <v>1051178</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>0</v>
+        <v>3517019</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>0</v>
+        <v>7019381</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>0</v>
+        <v>352586</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>0</v>
+        <v>703454</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>0</v>
+        <v>265025</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>0</v>
+        <v>528799</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>0</v>
+        <v>442383</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>0</v>
+        <v>883111</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>0</v>
+        <v>354111</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>0</v>
+        <v>707475</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>42244366</v>
+        <v>42473359</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>84483745</v>
+        <v>84942001</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>79833</v>
+        <v>80326</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>159993</v>
+        <v>160806</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>793516</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>1589894</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>527691</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>1057848</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>38947257</v>
+        <v>50110219</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>22041899</v>
+        <v>28169893</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>132705</v>
+        <v>6298781</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>263995</v>
+        <v>12615927</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>21909194</v>
+        <v>21871112</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>44001405</v>
+        <v>43764394</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>1313648</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>2625896</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>421167</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>841091</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>263865</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>526593</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>317429</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>633302</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>238582</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>476058</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>159280</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>317993</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>132792</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>265337</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>1061897</v>
+        <v>1061686</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>2111966</v>
+        <v>2123547</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>35040</v>
+        <v>35335</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>70402</v>
+        <v>70746</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>2206565</v>
+        <v>2203502</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>4399831</v>
+        <v>4415356</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>13185617</v>
+        <v>13187844</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>26401149</v>
+        <v>26438423</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>0</v>
+        <v>2192802</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>0</v>
+        <v>4396324</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>451279</v>
+        <v>447729</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>900036</v>
+        <v>897319</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>398227</v>
+        <v>397627</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>799976</v>
+        <v>796321</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>30166</v>
+        <v>29827</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>60001</v>
+        <v>59676</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>134379</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>268578</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>230395</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>460060</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>89984</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>179569</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>67655</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>134978</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>112992</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>225471</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>331872</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>662628</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>60359</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>120621</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>45235</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>90490</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>75267</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>150715</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>52566</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>105341</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>37453</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>75087</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>29894</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>59932</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>22383</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>44855</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>3376942</v>
+        <v>6352553</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>-87912</v>
+        <v>3960959</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>131422</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>262634</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>37413</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>74700</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>60297</v>
+        <v>60010</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>120003</v>
+        <v>119747</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>3316645</v>
+        <v>6423965</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>1810770</v>
+        <v>1808272</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>3599989</v>
+        <v>3608549</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>1505875</v>
+        <v>4615693</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>1505875</v>
+        <v>4615693</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>1505875</v>
+        <v>4615693</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>1505875</v>
+        <v>4615693</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>1505875</v>
+        <v>4615693</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
